--- a/data/trans_orig/IP29A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP29A_2023-Provincia-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.186778978895642</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.337191661887794</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.250912465334304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,7; 7,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 8,26</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,76; 7,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.703627836214469</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.568927430834723</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.764763726293513</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.090645940501735</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.25863337474197</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.070085309336834</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,32</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,39; 14,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,84; 13,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,18; 12,41</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>10.32073743714347</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>10.02966750613221</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>10.1881056789565</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,94</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7.389051090215391</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.837539139417708</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>8.180137760505916</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,99; 11,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,35; 9,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,16; 9,94</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.13536716797745</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>13.24006836455232</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12.40829594755344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +661,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10,22</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>8.937694625756922</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.689602134493447</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8.328610740409648</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 10,2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 15,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,53; 12,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.98676325603775</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.345320941649499</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.158337570129341</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.57722392717787</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.482202011242784</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.940813976212157</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>8,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>6,33; 16,65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5,55; 10,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 11,86</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>8.197484187651726</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>12.10697198163463</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>10.21965451427241</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.155937478769643</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>9.418206904990624</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.526084088872867</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>8,03; 11,64</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 11,19</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7,65; 10,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.19539142558519</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>15.6467099423658</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>12.42344766130702</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,147 +771,272 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>10,11</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,85</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,45</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>8.953665752627218</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.216466426693492</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8.11289291764761</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>8,39; 11,88</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 12,78</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9,23; 11,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.33110093880603</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5.553223648918501</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>6.499684447232979</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>16.64659097034461</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.53728577100224</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>11.86006651365977</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6,6</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6,74</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>4,81; 8,78</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 9,02</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 8,22</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>9.438386950122457</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8.227056487730158</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>8.887322660945783</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>8.027416194256269</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>6.586070320368442</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>7.653420340311589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>7,83; 9,48</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7,97; 9,64</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>8,16; 9,27</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>11.64255273170098</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>11.19344322084907</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>10.43579567601073</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>10.10547685536133</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>10.84608993245309</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>10.44700213179974</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>8.38961709305479</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>9.324494865291088</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>9.23130079769688</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>11.88397133120772</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>12.77869677152769</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>11.66222552534324</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>6.600745568623221</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>6.744536786490037</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>6.670151024208679</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>4.81360956752203</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>4.966881491605727</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>5.46230810342862</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>8.781062329956546</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>9.022111704998235</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>8.218169714075282</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>8.611731252568058</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>8.765682518218622</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>8.684056477964486</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>7.833070151589217</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>7.969775667232789</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>8.155318453215974</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>9.483729182055642</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>9.642100439127596</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>9.270677110871977</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -994,16 +1044,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
